--- a/hypatia/examples/Atlantis/parameters/parameters_reg1 - maxlanduse.xlsx
+++ b/hypatia/examples/Atlantis/parameters/parameters_reg1 - maxlanduse.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SESAM\Documents\Hypatia-polimi-main\hypatia\examples\Atlantis\parameters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polimi365-my.sharepoint.com/personal/10394890_polimi_it/Documents/Research/Repositories/Hypatia-polimi/hypatia/examples/Atlantis-1Region/parameters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C0EC49-3DB9-4ADF-9CBC-536CB7B9B8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{B9C0EC49-3DB9-4ADF-9CBC-536CB7B9B8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED556BBB-70FA-47CF-9FBD-BC3F3054F03B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" firstSheet="27" activeTab="34" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F_OM" sheetId="1" r:id="rId1"/>
@@ -264,7 +264,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -565,16 +565,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" customWidth="1"/>
+    <col min="4" max="4" width="16.1796875" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -589,7 +589,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -606,12 +606,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -629,7 +629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -647,7 +647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -665,7 +665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -683,7 +683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -701,7 +701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -719,7 +719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -737,7 +737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -755,7 +755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -773,7 +773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -802,13 +802,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="5" width="11.42578125" customWidth="1"/>
+    <col min="2" max="5" width="11.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -823,7 +823,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -840,12 +840,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -864,7 +864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -883,7 +883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -902,7 +902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -940,7 +940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -997,7 +997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -1046,9 +1046,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
@@ -1065,7 +1065,7 @@
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1090,7 +1090,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1119,12 +1119,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1269,7 +1269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -1428,9 +1428,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1462,12 +1462,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -1648,12 +1648,12 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="22.5703125" customWidth="1"/>
+    <col min="2" max="2" width="22.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -1709,7 +1709,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -1717,7 +1717,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -1749,9 +1749,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1783,12 +1783,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -1816,12 +1816,12 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="5" width="16.5703125" customWidth="1"/>
+    <col min="1" max="5" width="16.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1853,12 +1853,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>29</v>
       </c>
@@ -1886,13 +1886,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.42578125" customWidth="1"/>
-    <col min="2" max="6" width="18.5703125" customWidth="1"/>
+    <col min="1" max="1" width="29.453125" customWidth="1"/>
+    <col min="2" max="6" width="18.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1924,12 +1924,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>30</v>
       </c>
@@ -1957,12 +1957,12 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1977,7 +1977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1994,12 +1994,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
@@ -2027,9 +2027,9 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C241"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="4"/>
       <c r="B3" s="1">
         <v>2</v>
@@ -2062,7 +2062,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
       <c r="B4" s="1">
         <v>3</v>
@@ -2072,7 +2072,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
       <c r="B5" s="1">
         <v>4</v>
@@ -2082,7 +2082,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
       <c r="B6" s="1">
         <v>5</v>
@@ -2092,7 +2092,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
       <c r="B7" s="1">
         <v>6</v>
@@ -2102,7 +2102,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
       <c r="B8" s="1">
         <v>7</v>
@@ -2112,7 +2112,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="4"/>
       <c r="B9" s="1">
         <v>8</v>
@@ -2122,7 +2122,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="4"/>
       <c r="B10" s="1">
         <v>9</v>
@@ -2132,7 +2132,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="4"/>
       <c r="B11" s="1">
         <v>10</v>
@@ -2142,7 +2142,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="4"/>
       <c r="B12" s="1">
         <v>11</v>
@@ -2152,7 +2152,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="4"/>
       <c r="B13" s="1">
         <v>12</v>
@@ -2162,7 +2162,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="4"/>
       <c r="B14" s="1">
         <v>13</v>
@@ -2172,7 +2172,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="4"/>
       <c r="B15" s="1">
         <v>14</v>
@@ -2182,7 +2182,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="4"/>
       <c r="B16" s="1">
         <v>15</v>
@@ -2192,7 +2192,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="4"/>
       <c r="B17" s="1">
         <v>16</v>
@@ -2202,7 +2202,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="4"/>
       <c r="B18" s="1">
         <v>17</v>
@@ -2212,7 +2212,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="4"/>
       <c r="B19" s="1">
         <v>18</v>
@@ -2222,7 +2222,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="4"/>
       <c r="B20" s="1">
         <v>19</v>
@@ -2232,7 +2232,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="4"/>
       <c r="B21" s="1">
         <v>20</v>
@@ -2242,7 +2242,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="4"/>
       <c r="B22" s="1">
         <v>21</v>
@@ -2252,7 +2252,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="4"/>
       <c r="B23" s="1">
         <v>22</v>
@@ -2262,7 +2262,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="4"/>
       <c r="B24" s="1">
         <v>23</v>
@@ -2272,7 +2272,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="4"/>
       <c r="B25" s="1">
         <v>24</v>
@@ -2282,7 +2282,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>11</v>
       </c>
@@ -2294,7 +2294,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="4"/>
       <c r="B27" s="1">
         <v>2</v>
@@ -2304,7 +2304,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="4"/>
       <c r="B28" s="1">
         <v>3</v>
@@ -2314,7 +2314,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="4"/>
       <c r="B29" s="1">
         <v>4</v>
@@ -2324,7 +2324,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="4"/>
       <c r="B30" s="1">
         <v>5</v>
@@ -2334,7 +2334,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="4"/>
       <c r="B31" s="1">
         <v>6</v>
@@ -2344,7 +2344,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="4"/>
       <c r="B32" s="1">
         <v>7</v>
@@ -2354,7 +2354,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="4"/>
       <c r="B33" s="1">
         <v>8</v>
@@ -2364,7 +2364,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="4"/>
       <c r="B34" s="1">
         <v>9</v>
@@ -2374,7 +2374,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="4"/>
       <c r="B35" s="1">
         <v>10</v>
@@ -2384,7 +2384,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="4"/>
       <c r="B36" s="1">
         <v>11</v>
@@ -2394,7 +2394,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="4"/>
       <c r="B37" s="1">
         <v>12</v>
@@ -2404,7 +2404,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="4"/>
       <c r="B38" s="1">
         <v>13</v>
@@ -2414,7 +2414,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="4"/>
       <c r="B39" s="1">
         <v>14</v>
@@ -2424,7 +2424,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="4"/>
       <c r="B40" s="1">
         <v>15</v>
@@ -2434,7 +2434,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="4"/>
       <c r="B41" s="1">
         <v>16</v>
@@ -2444,7 +2444,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="4"/>
       <c r="B42" s="1">
         <v>17</v>
@@ -2454,7 +2454,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="4"/>
       <c r="B43" s="1">
         <v>18</v>
@@ -2464,7 +2464,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="4"/>
       <c r="B44" s="1">
         <v>19</v>
@@ -2474,7 +2474,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="4"/>
       <c r="B45" s="1">
         <v>20</v>
@@ -2484,7 +2484,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="4"/>
       <c r="B46" s="1">
         <v>21</v>
@@ -2494,7 +2494,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="4"/>
       <c r="B47" s="1">
         <v>22</v>
@@ -2504,7 +2504,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="4"/>
       <c r="B48" s="1">
         <v>23</v>
@@ -2514,7 +2514,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="4"/>
       <c r="B49" s="1">
         <v>24</v>
@@ -2524,7 +2524,7 @@
         <v>333.33333333333331</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>12</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="4"/>
       <c r="B51" s="1">
         <v>2</v>
@@ -2546,7 +2546,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="4"/>
       <c r="B52" s="1">
         <v>3</v>
@@ -2556,7 +2556,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="4"/>
       <c r="B53" s="1">
         <v>4</v>
@@ -2566,7 +2566,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="4"/>
       <c r="B54" s="1">
         <v>5</v>
@@ -2576,7 +2576,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="4"/>
       <c r="B55" s="1">
         <v>6</v>
@@ -2586,7 +2586,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="4"/>
       <c r="B56" s="1">
         <v>7</v>
@@ -2596,7 +2596,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="4"/>
       <c r="B57" s="1">
         <v>8</v>
@@ -2606,7 +2606,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="4"/>
       <c r="B58" s="1">
         <v>9</v>
@@ -2616,7 +2616,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="4"/>
       <c r="B59" s="1">
         <v>10</v>
@@ -2626,7 +2626,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="4"/>
       <c r="B60" s="1">
         <v>11</v>
@@ -2636,7 +2636,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="4"/>
       <c r="B61" s="1">
         <v>12</v>
@@ -2646,7 +2646,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="4"/>
       <c r="B62" s="1">
         <v>13</v>
@@ -2656,7 +2656,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="4"/>
       <c r="B63" s="1">
         <v>14</v>
@@ -2666,7 +2666,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="4"/>
       <c r="B64" s="1">
         <v>15</v>
@@ -2676,7 +2676,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="4"/>
       <c r="B65" s="1">
         <v>16</v>
@@ -2686,7 +2686,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="4"/>
       <c r="B66" s="1">
         <v>17</v>
@@ -2696,7 +2696,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="4"/>
       <c r="B67" s="1">
         <v>18</v>
@@ -2706,7 +2706,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="4"/>
       <c r="B68" s="1">
         <v>19</v>
@@ -2716,7 +2716,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="4"/>
       <c r="B69" s="1">
         <v>20</v>
@@ -2726,7 +2726,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="4"/>
       <c r="B70" s="1">
         <v>21</v>
@@ -2736,7 +2736,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="4"/>
       <c r="B71" s="1">
         <v>22</v>
@@ -2746,7 +2746,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="4"/>
       <c r="B72" s="1">
         <v>23</v>
@@ -2756,7 +2756,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="4"/>
       <c r="B73" s="1">
         <v>24</v>
@@ -2766,7 +2766,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
         <v>13</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="4"/>
       <c r="B75" s="1">
         <v>2</v>
@@ -2788,7 +2788,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="4"/>
       <c r="B76" s="1">
         <v>3</v>
@@ -2798,7 +2798,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="4"/>
       <c r="B77" s="1">
         <v>4</v>
@@ -2808,7 +2808,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="4"/>
       <c r="B78" s="1">
         <v>5</v>
@@ -2818,7 +2818,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="4"/>
       <c r="B79" s="1">
         <v>6</v>
@@ -2828,7 +2828,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="4"/>
       <c r="B80" s="1">
         <v>7</v>
@@ -2838,7 +2838,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="4"/>
       <c r="B81" s="1">
         <v>8</v>
@@ -2848,7 +2848,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="4"/>
       <c r="B82" s="1">
         <v>9</v>
@@ -2858,7 +2858,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="4"/>
       <c r="B83" s="1">
         <v>10</v>
@@ -2868,7 +2868,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="4"/>
       <c r="B84" s="1">
         <v>11</v>
@@ -2878,7 +2878,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="4"/>
       <c r="B85" s="1">
         <v>12</v>
@@ -2888,7 +2888,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="4"/>
       <c r="B86" s="1">
         <v>13</v>
@@ -2898,7 +2898,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="4"/>
       <c r="B87" s="1">
         <v>14</v>
@@ -2908,7 +2908,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="4"/>
       <c r="B88" s="1">
         <v>15</v>
@@ -2918,7 +2918,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="4"/>
       <c r="B89" s="1">
         <v>16</v>
@@ -2928,7 +2928,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="4"/>
       <c r="B90" s="1">
         <v>17</v>
@@ -2938,7 +2938,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="4"/>
       <c r="B91" s="1">
         <v>18</v>
@@ -2948,7 +2948,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="4"/>
       <c r="B92" s="1">
         <v>19</v>
@@ -2958,7 +2958,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="4"/>
       <c r="B93" s="1">
         <v>20</v>
@@ -2968,7 +2968,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="4"/>
       <c r="B94" s="1">
         <v>21</v>
@@ -2978,7 +2978,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="4"/>
       <c r="B95" s="1">
         <v>22</v>
@@ -2988,7 +2988,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="4"/>
       <c r="B96" s="1">
         <v>23</v>
@@ -2998,7 +2998,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="4"/>
       <c r="B97" s="1">
         <v>24</v>
@@ -3008,7 +3008,7 @@
         <v>416.66666666666669</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
         <v>14</v>
       </c>
@@ -3020,7 +3020,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="4"/>
       <c r="B99" s="1">
         <v>2</v>
@@ -3030,7 +3030,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="4"/>
       <c r="B100" s="1">
         <v>3</v>
@@ -3040,7 +3040,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="4"/>
       <c r="B101" s="1">
         <v>4</v>
@@ -3050,7 +3050,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="4"/>
       <c r="B102" s="1">
         <v>5</v>
@@ -3060,7 +3060,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="4"/>
       <c r="B103" s="1">
         <v>6</v>
@@ -3070,7 +3070,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="4"/>
       <c r="B104" s="1">
         <v>7</v>
@@ -3080,7 +3080,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="4"/>
       <c r="B105" s="1">
         <v>8</v>
@@ -3090,7 +3090,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="4"/>
       <c r="B106" s="1">
         <v>9</v>
@@ -3100,7 +3100,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="4"/>
       <c r="B107" s="1">
         <v>10</v>
@@ -3110,7 +3110,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="4"/>
       <c r="B108" s="1">
         <v>11</v>
@@ -3120,7 +3120,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="4"/>
       <c r="B109" s="1">
         <v>12</v>
@@ -3130,7 +3130,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="4"/>
       <c r="B110" s="1">
         <v>13</v>
@@ -3140,7 +3140,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="4"/>
       <c r="B111" s="1">
         <v>14</v>
@@ -3150,7 +3150,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="4"/>
       <c r="B112" s="1">
         <v>15</v>
@@ -3160,7 +3160,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="4"/>
       <c r="B113" s="1">
         <v>16</v>
@@ -3170,7 +3170,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="4"/>
       <c r="B114" s="1">
         <v>17</v>
@@ -3180,7 +3180,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="4"/>
       <c r="B115" s="1">
         <v>18</v>
@@ -3190,7 +3190,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="4"/>
       <c r="B116" s="1">
         <v>19</v>
@@ -3200,7 +3200,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="4"/>
       <c r="B117" s="1">
         <v>20</v>
@@ -3210,7 +3210,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="4"/>
       <c r="B118" s="1">
         <v>21</v>
@@ -3220,7 +3220,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="4"/>
       <c r="B119" s="1">
         <v>22</v>
@@ -3230,7 +3230,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="4"/>
       <c r="B120" s="1">
         <v>23</v>
@@ -3240,7 +3240,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="4"/>
       <c r="B121" s="1">
         <v>24</v>
@@ -3250,7 +3250,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
         <v>15</v>
       </c>
@@ -3262,7 +3262,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="4"/>
       <c r="B123" s="1">
         <v>2</v>
@@ -3272,7 +3272,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="4"/>
       <c r="B124" s="1">
         <v>3</v>
@@ -3282,7 +3282,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="4"/>
       <c r="B125" s="1">
         <v>4</v>
@@ -3292,7 +3292,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="4"/>
       <c r="B126" s="1">
         <v>5</v>
@@ -3302,7 +3302,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="4"/>
       <c r="B127" s="1">
         <v>6</v>
@@ -3312,7 +3312,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="4"/>
       <c r="B128" s="1">
         <v>7</v>
@@ -3322,7 +3322,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="4"/>
       <c r="B129" s="1">
         <v>8</v>
@@ -3332,7 +3332,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="4"/>
       <c r="B130" s="1">
         <v>9</v>
@@ -3342,7 +3342,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="4"/>
       <c r="B131" s="1">
         <v>10</v>
@@ -3352,7 +3352,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="4"/>
       <c r="B132" s="1">
         <v>11</v>
@@ -3362,7 +3362,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="4"/>
       <c r="B133" s="1">
         <v>12</v>
@@ -3372,7 +3372,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="4"/>
       <c r="B134" s="1">
         <v>13</v>
@@ -3382,7 +3382,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="4"/>
       <c r="B135" s="1">
         <v>14</v>
@@ -3392,7 +3392,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="4"/>
       <c r="B136" s="1">
         <v>15</v>
@@ -3402,7 +3402,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="4"/>
       <c r="B137" s="1">
         <v>16</v>
@@ -3412,7 +3412,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="4"/>
       <c r="B138" s="1">
         <v>17</v>
@@ -3422,7 +3422,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="4"/>
       <c r="B139" s="1">
         <v>18</v>
@@ -3432,7 +3432,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="4"/>
       <c r="B140" s="1">
         <v>19</v>
@@ -3442,7 +3442,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="4"/>
       <c r="B141" s="1">
         <v>20</v>
@@ -3452,7 +3452,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="4"/>
       <c r="B142" s="1">
         <v>21</v>
@@ -3462,7 +3462,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="4"/>
       <c r="B143" s="1">
         <v>22</v>
@@ -3472,7 +3472,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="4"/>
       <c r="B144" s="1">
         <v>23</v>
@@ -3482,7 +3482,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="4"/>
       <c r="B145" s="1">
         <v>24</v>
@@ -3492,7 +3492,7 @@
         <v>541.66666666666663</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
         <v>16</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="4"/>
       <c r="B147" s="1">
         <v>2</v>
@@ -3514,7 +3514,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="4"/>
       <c r="B148" s="1">
         <v>3</v>
@@ -3524,7 +3524,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="4"/>
       <c r="B149" s="1">
         <v>4</v>
@@ -3534,7 +3534,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="4"/>
       <c r="B150" s="1">
         <v>5</v>
@@ -3544,7 +3544,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" s="4"/>
       <c r="B151" s="1">
         <v>6</v>
@@ -3554,7 +3554,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="4"/>
       <c r="B152" s="1">
         <v>7</v>
@@ -3564,7 +3564,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="4"/>
       <c r="B153" s="1">
         <v>8</v>
@@ -3574,7 +3574,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="4"/>
       <c r="B154" s="1">
         <v>9</v>
@@ -3584,7 +3584,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="4"/>
       <c r="B155" s="1">
         <v>10</v>
@@ -3594,7 +3594,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="4"/>
       <c r="B156" s="1">
         <v>11</v>
@@ -3604,7 +3604,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="4"/>
       <c r="B157" s="1">
         <v>12</v>
@@ -3614,7 +3614,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="4"/>
       <c r="B158" s="1">
         <v>13</v>
@@ -3624,7 +3624,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="4"/>
       <c r="B159" s="1">
         <v>14</v>
@@ -3634,7 +3634,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="4"/>
       <c r="B160" s="1">
         <v>15</v>
@@ -3644,7 +3644,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" s="4"/>
       <c r="B161" s="1">
         <v>16</v>
@@ -3654,7 +3654,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" s="4"/>
       <c r="B162" s="1">
         <v>17</v>
@@ -3664,7 +3664,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" s="4"/>
       <c r="B163" s="1">
         <v>18</v>
@@ -3674,7 +3674,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" s="4"/>
       <c r="B164" s="1">
         <v>19</v>
@@ -3684,7 +3684,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" s="4"/>
       <c r="B165" s="1">
         <v>20</v>
@@ -3694,7 +3694,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" s="4"/>
       <c r="B166" s="1">
         <v>21</v>
@@ -3704,7 +3704,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" s="4"/>
       <c r="B167" s="1">
         <v>22</v>
@@ -3714,7 +3714,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" s="4"/>
       <c r="B168" s="1">
         <v>23</v>
@@ -3724,7 +3724,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" s="4"/>
       <c r="B169" s="1">
         <v>24</v>
@@ -3734,7 +3734,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
         <v>17</v>
       </c>
@@ -3746,7 +3746,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" s="4"/>
       <c r="B171" s="1">
         <v>2</v>
@@ -3756,7 +3756,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" s="4"/>
       <c r="B172" s="1">
         <v>3</v>
@@ -3766,7 +3766,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" s="4"/>
       <c r="B173" s="1">
         <v>4</v>
@@ -3776,7 +3776,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" s="4"/>
       <c r="B174" s="1">
         <v>5</v>
@@ -3786,7 +3786,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" s="4"/>
       <c r="B175" s="1">
         <v>6</v>
@@ -3796,7 +3796,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" s="4"/>
       <c r="B176" s="1">
         <v>7</v>
@@ -3806,7 +3806,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" s="4"/>
       <c r="B177" s="1">
         <v>8</v>
@@ -3816,7 +3816,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" s="4"/>
       <c r="B178" s="1">
         <v>9</v>
@@ -3826,7 +3826,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" s="4"/>
       <c r="B179" s="1">
         <v>10</v>
@@ -3836,7 +3836,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" s="4"/>
       <c r="B180" s="1">
         <v>11</v>
@@ -3846,7 +3846,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" s="4"/>
       <c r="B181" s="1">
         <v>12</v>
@@ -3856,7 +3856,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" s="4"/>
       <c r="B182" s="1">
         <v>13</v>
@@ -3866,7 +3866,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" s="4"/>
       <c r="B183" s="1">
         <v>14</v>
@@ -3876,7 +3876,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" s="4"/>
       <c r="B184" s="1">
         <v>15</v>
@@ -3886,7 +3886,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" s="4"/>
       <c r="B185" s="1">
         <v>16</v>
@@ -3896,7 +3896,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" s="4"/>
       <c r="B186" s="1">
         <v>17</v>
@@ -3906,7 +3906,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" s="4"/>
       <c r="B187" s="1">
         <v>18</v>
@@ -3916,7 +3916,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" s="4"/>
       <c r="B188" s="1">
         <v>19</v>
@@ -3926,7 +3926,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" s="4"/>
       <c r="B189" s="1">
         <v>20</v>
@@ -3936,7 +3936,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" s="4"/>
       <c r="B190" s="1">
         <v>21</v>
@@ -3946,7 +3946,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" s="4"/>
       <c r="B191" s="1">
         <v>22</v>
@@ -3956,7 +3956,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" s="4"/>
       <c r="B192" s="1">
         <v>23</v>
@@ -3966,7 +3966,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" s="4"/>
       <c r="B193" s="1">
         <v>24</v>
@@ -3976,7 +3976,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" s="4" t="s">
         <v>18</v>
       </c>
@@ -3988,7 +3988,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" s="4"/>
       <c r="B195" s="1">
         <v>2</v>
@@ -3998,7 +3998,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" s="4"/>
       <c r="B196" s="1">
         <v>3</v>
@@ -4008,7 +4008,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" s="4"/>
       <c r="B197" s="1">
         <v>4</v>
@@ -4018,7 +4018,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" s="4"/>
       <c r="B198" s="1">
         <v>5</v>
@@ -4028,7 +4028,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" s="4"/>
       <c r="B199" s="1">
         <v>6</v>
@@ -4038,7 +4038,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" s="4"/>
       <c r="B200" s="1">
         <v>7</v>
@@ -4048,7 +4048,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" s="4"/>
       <c r="B201" s="1">
         <v>8</v>
@@ -4058,7 +4058,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" s="4"/>
       <c r="B202" s="1">
         <v>9</v>
@@ -4068,7 +4068,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" s="4"/>
       <c r="B203" s="1">
         <v>10</v>
@@ -4078,7 +4078,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" s="4"/>
       <c r="B204" s="1">
         <v>11</v>
@@ -4088,7 +4088,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" s="4"/>
       <c r="B205" s="1">
         <v>12</v>
@@ -4098,7 +4098,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" s="4"/>
       <c r="B206" s="1">
         <v>13</v>
@@ -4108,7 +4108,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" s="4"/>
       <c r="B207" s="1">
         <v>14</v>
@@ -4118,7 +4118,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" s="4"/>
       <c r="B208" s="1">
         <v>15</v>
@@ -4128,7 +4128,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" s="4"/>
       <c r="B209" s="1">
         <v>16</v>
@@ -4138,7 +4138,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" s="4"/>
       <c r="B210" s="1">
         <v>17</v>
@@ -4148,7 +4148,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" s="4"/>
       <c r="B211" s="1">
         <v>18</v>
@@ -4158,7 +4158,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" s="4"/>
       <c r="B212" s="1">
         <v>19</v>
@@ -4168,7 +4168,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" s="4"/>
       <c r="B213" s="1">
         <v>20</v>
@@ -4178,7 +4178,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" s="4"/>
       <c r="B214" s="1">
         <v>21</v>
@@ -4188,7 +4188,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" s="4"/>
       <c r="B215" s="1">
         <v>22</v>
@@ -4198,7 +4198,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" s="4"/>
       <c r="B216" s="1">
         <v>23</v>
@@ -4208,7 +4208,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" s="4"/>
       <c r="B217" s="1">
         <v>24</v>
@@ -4218,7 +4218,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" s="4" t="s">
         <v>19</v>
       </c>
@@ -4230,7 +4230,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219" s="4"/>
       <c r="B219" s="1">
         <v>2</v>
@@ -4240,7 +4240,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220" s="4"/>
       <c r="B220" s="1">
         <v>3</v>
@@ -4250,7 +4250,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" s="4"/>
       <c r="B221" s="1">
         <v>4</v>
@@ -4260,7 +4260,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222" s="4"/>
       <c r="B222" s="1">
         <v>5</v>
@@ -4270,7 +4270,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" s="4"/>
       <c r="B223" s="1">
         <v>6</v>
@@ -4280,7 +4280,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" s="4"/>
       <c r="B224" s="1">
         <v>7</v>
@@ -4290,7 +4290,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" s="4"/>
       <c r="B225" s="1">
         <v>8</v>
@@ -4300,7 +4300,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226" s="4"/>
       <c r="B226" s="1">
         <v>9</v>
@@ -4310,7 +4310,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" s="4"/>
       <c r="B227" s="1">
         <v>10</v>
@@ -4320,7 +4320,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" s="4"/>
       <c r="B228" s="1">
         <v>11</v>
@@ -4330,7 +4330,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" s="4"/>
       <c r="B229" s="1">
         <v>12</v>
@@ -4340,7 +4340,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" s="4"/>
       <c r="B230" s="1">
         <v>13</v>
@@ -4350,7 +4350,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" s="4"/>
       <c r="B231" s="1">
         <v>14</v>
@@ -4360,7 +4360,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" s="4"/>
       <c r="B232" s="1">
         <v>15</v>
@@ -4370,7 +4370,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" s="4"/>
       <c r="B233" s="1">
         <v>16</v>
@@ -4380,7 +4380,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" s="4"/>
       <c r="B234" s="1">
         <v>17</v>
@@ -4390,7 +4390,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" s="4"/>
       <c r="B235" s="1">
         <v>18</v>
@@ -4400,7 +4400,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" s="4"/>
       <c r="B236" s="1">
         <v>19</v>
@@ -4410,7 +4410,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" s="4"/>
       <c r="B237" s="1">
         <v>20</v>
@@ -4420,7 +4420,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238" s="4"/>
       <c r="B238" s="1">
         <v>21</v>
@@ -4430,7 +4430,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" s="4"/>
       <c r="B239" s="1">
         <v>22</v>
@@ -4440,7 +4440,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" s="4"/>
       <c r="B240" s="1">
         <v>23</v>
@@ -4450,7 +4450,7 @@
         <v>666.66666666666663</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" s="4"/>
       <c r="B241" s="1">
         <v>24</v>
@@ -4480,13 +4480,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4501,7 +4501,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -4518,12 +4518,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -4540,7 +4540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -4557,7 +4557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -4591,7 +4591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -4625,7 +4625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -4642,7 +4642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -4659,7 +4659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -4676,7 +4676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -4704,12 +4704,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="5" width="21.140625" customWidth="1"/>
+    <col min="1" max="5" width="21.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4724,7 +4724,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -4741,12 +4741,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -4764,7 +4764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -4836,7 +4836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -4854,7 +4854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -4872,7 +4872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -4890,7 +4890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -4908,7 +4908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -4937,9 +4937,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4954,7 +4954,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -4971,12 +4971,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -5010,7 +5010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -5044,7 +5044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -5095,7 +5095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -5112,7 +5112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -5129,7 +5129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -5157,9 +5157,9 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5174,7 +5174,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -5191,12 +5191,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -5213,7 +5213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -5230,7 +5230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -5247,7 +5247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -5264,7 +5264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -5281,7 +5281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -5298,7 +5298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -5315,7 +5315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -5332,7 +5332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -5349,7 +5349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -5377,12 +5377,12 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:F243"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="7" width="13.140625" customWidth="1"/>
+    <col min="2" max="7" width="13.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5397,7 +5397,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -5414,7 +5414,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -5422,7 +5422,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
@@ -5442,7 +5442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
       <c r="B5" s="1">
         <v>2</v>
@@ -5460,7 +5460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
       <c r="B6" s="1">
         <v>3</v>
@@ -5478,7 +5478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
       <c r="B7" s="1">
         <v>4</v>
@@ -5496,7 +5496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
       <c r="B8" s="1">
         <v>5</v>
@@ -5514,7 +5514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="4"/>
       <c r="B9" s="1">
         <v>6</v>
@@ -5532,7 +5532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="4"/>
       <c r="B10" s="1">
         <v>7</v>
@@ -5550,7 +5550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="4"/>
       <c r="B11" s="1">
         <v>8</v>
@@ -5568,7 +5568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="4"/>
       <c r="B12" s="1">
         <v>9</v>
@@ -5586,7 +5586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="4"/>
       <c r="B13" s="1">
         <v>10</v>
@@ -5604,7 +5604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="4"/>
       <c r="B14" s="1">
         <v>11</v>
@@ -5622,7 +5622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="4"/>
       <c r="B15" s="1">
         <v>12</v>
@@ -5640,7 +5640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="4"/>
       <c r="B16" s="1">
         <v>13</v>
@@ -5658,7 +5658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="4"/>
       <c r="B17" s="1">
         <v>14</v>
@@ -5676,7 +5676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="4"/>
       <c r="B18" s="1">
         <v>15</v>
@@ -5694,7 +5694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="4"/>
       <c r="B19" s="1">
         <v>16</v>
@@ -5712,7 +5712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="4"/>
       <c r="B20" s="1">
         <v>17</v>
@@ -5730,7 +5730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="4"/>
       <c r="B21" s="1">
         <v>18</v>
@@ -5748,7 +5748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="4"/>
       <c r="B22" s="1">
         <v>19</v>
@@ -5766,7 +5766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="4"/>
       <c r="B23" s="1">
         <v>20</v>
@@ -5784,7 +5784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="4"/>
       <c r="B24" s="1">
         <v>21</v>
@@ -5802,7 +5802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="4"/>
       <c r="B25" s="1">
         <v>22</v>
@@ -5820,7 +5820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="4"/>
       <c r="B26" s="1">
         <v>23</v>
@@ -5838,7 +5838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="4"/>
       <c r="B27" s="1">
         <v>24</v>
@@ -5856,7 +5856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>11</v>
       </c>
@@ -5876,7 +5876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="4"/>
       <c r="B29" s="1">
         <v>2</v>
@@ -5894,7 +5894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="4"/>
       <c r="B30" s="1">
         <v>3</v>
@@ -5912,7 +5912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="4"/>
       <c r="B31" s="1">
         <v>4</v>
@@ -5930,7 +5930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="4"/>
       <c r="B32" s="1">
         <v>5</v>
@@ -5948,7 +5948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="4"/>
       <c r="B33" s="1">
         <v>6</v>
@@ -5966,7 +5966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="4"/>
       <c r="B34" s="1">
         <v>7</v>
@@ -5984,7 +5984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="4"/>
       <c r="B35" s="1">
         <v>8</v>
@@ -6002,7 +6002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="4"/>
       <c r="B36" s="1">
         <v>9</v>
@@ -6020,7 +6020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="4"/>
       <c r="B37" s="1">
         <v>10</v>
@@ -6038,7 +6038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="4"/>
       <c r="B38" s="1">
         <v>11</v>
@@ -6056,7 +6056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="4"/>
       <c r="B39" s="1">
         <v>12</v>
@@ -6074,7 +6074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="4"/>
       <c r="B40" s="1">
         <v>13</v>
@@ -6092,7 +6092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="4"/>
       <c r="B41" s="1">
         <v>14</v>
@@ -6110,7 +6110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="4"/>
       <c r="B42" s="1">
         <v>15</v>
@@ -6128,7 +6128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="4"/>
       <c r="B43" s="1">
         <v>16</v>
@@ -6146,7 +6146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="4"/>
       <c r="B44" s="1">
         <v>17</v>
@@ -6164,7 +6164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="4"/>
       <c r="B45" s="1">
         <v>18</v>
@@ -6182,7 +6182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="4"/>
       <c r="B46" s="1">
         <v>19</v>
@@ -6200,7 +6200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="4"/>
       <c r="B47" s="1">
         <v>20</v>
@@ -6218,7 +6218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="4"/>
       <c r="B48" s="1">
         <v>21</v>
@@ -6236,7 +6236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="4"/>
       <c r="B49" s="1">
         <v>22</v>
@@ -6254,7 +6254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="4"/>
       <c r="B50" s="1">
         <v>23</v>
@@ -6272,7 +6272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="4"/>
       <c r="B51" s="1">
         <v>24</v>
@@ -6290,7 +6290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>12</v>
       </c>
@@ -6310,7 +6310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="4"/>
       <c r="B53" s="1">
         <v>2</v>
@@ -6328,7 +6328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="4"/>
       <c r="B54" s="1">
         <v>3</v>
@@ -6346,7 +6346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="4"/>
       <c r="B55" s="1">
         <v>4</v>
@@ -6364,7 +6364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="4"/>
       <c r="B56" s="1">
         <v>5</v>
@@ -6382,7 +6382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="4"/>
       <c r="B57" s="1">
         <v>6</v>
@@ -6400,7 +6400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="4"/>
       <c r="B58" s="1">
         <v>7</v>
@@ -6418,7 +6418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="4"/>
       <c r="B59" s="1">
         <v>8</v>
@@ -6436,7 +6436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="4"/>
       <c r="B60" s="1">
         <v>9</v>
@@ -6454,7 +6454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="4"/>
       <c r="B61" s="1">
         <v>10</v>
@@ -6472,7 +6472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="4"/>
       <c r="B62" s="1">
         <v>11</v>
@@ -6490,7 +6490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="4"/>
       <c r="B63" s="1">
         <v>12</v>
@@ -6508,7 +6508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="4"/>
       <c r="B64" s="1">
         <v>13</v>
@@ -6526,7 +6526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="4"/>
       <c r="B65" s="1">
         <v>14</v>
@@ -6544,7 +6544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="4"/>
       <c r="B66" s="1">
         <v>15</v>
@@ -6562,7 +6562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="4"/>
       <c r="B67" s="1">
         <v>16</v>
@@ -6580,7 +6580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="4"/>
       <c r="B68" s="1">
         <v>17</v>
@@ -6598,7 +6598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="4"/>
       <c r="B69" s="1">
         <v>18</v>
@@ -6616,7 +6616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="4"/>
       <c r="B70" s="1">
         <v>19</v>
@@ -6634,7 +6634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="4"/>
       <c r="B71" s="1">
         <v>20</v>
@@ -6652,7 +6652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="4"/>
       <c r="B72" s="1">
         <v>21</v>
@@ -6670,7 +6670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="4"/>
       <c r="B73" s="1">
         <v>22</v>
@@ -6688,7 +6688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="4"/>
       <c r="B74" s="1">
         <v>23</v>
@@ -6706,7 +6706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="4"/>
       <c r="B75" s="1">
         <v>24</v>
@@ -6724,7 +6724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>13</v>
       </c>
@@ -6744,7 +6744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="4"/>
       <c r="B77" s="1">
         <v>2</v>
@@ -6762,7 +6762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="4"/>
       <c r="B78" s="1">
         <v>3</v>
@@ -6780,7 +6780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="4"/>
       <c r="B79" s="1">
         <v>4</v>
@@ -6798,7 +6798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="4"/>
       <c r="B80" s="1">
         <v>5</v>
@@ -6816,7 +6816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="4"/>
       <c r="B81" s="1">
         <v>6</v>
@@ -6834,7 +6834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="4"/>
       <c r="B82" s="1">
         <v>7</v>
@@ -6852,7 +6852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="4"/>
       <c r="B83" s="1">
         <v>8</v>
@@ -6870,7 +6870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="4"/>
       <c r="B84" s="1">
         <v>9</v>
@@ -6888,7 +6888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="4"/>
       <c r="B85" s="1">
         <v>10</v>
@@ -6906,7 +6906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="4"/>
       <c r="B86" s="1">
         <v>11</v>
@@ -6924,7 +6924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="4"/>
       <c r="B87" s="1">
         <v>12</v>
@@ -6942,7 +6942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="4"/>
       <c r="B88" s="1">
         <v>13</v>
@@ -6960,7 +6960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="4"/>
       <c r="B89" s="1">
         <v>14</v>
@@ -6978,7 +6978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="4"/>
       <c r="B90" s="1">
         <v>15</v>
@@ -6996,7 +6996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="4"/>
       <c r="B91" s="1">
         <v>16</v>
@@ -7014,7 +7014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="4"/>
       <c r="B92" s="1">
         <v>17</v>
@@ -7032,7 +7032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="4"/>
       <c r="B93" s="1">
         <v>18</v>
@@ -7050,7 +7050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="4"/>
       <c r="B94" s="1">
         <v>19</v>
@@ -7068,7 +7068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="4"/>
       <c r="B95" s="1">
         <v>20</v>
@@ -7086,7 +7086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="4"/>
       <c r="B96" s="1">
         <v>21</v>
@@ -7104,7 +7104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="4"/>
       <c r="B97" s="1">
         <v>22</v>
@@ -7122,7 +7122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="4"/>
       <c r="B98" s="1">
         <v>23</v>
@@ -7140,7 +7140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="4"/>
       <c r="B99" s="1">
         <v>24</v>
@@ -7158,7 +7158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
         <v>14</v>
       </c>
@@ -7178,7 +7178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="4"/>
       <c r="B101" s="1">
         <v>2</v>
@@ -7196,7 +7196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="4"/>
       <c r="B102" s="1">
         <v>3</v>
@@ -7214,7 +7214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="4"/>
       <c r="B103" s="1">
         <v>4</v>
@@ -7232,7 +7232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="4"/>
       <c r="B104" s="1">
         <v>5</v>
@@ -7250,7 +7250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="4"/>
       <c r="B105" s="1">
         <v>6</v>
@@ -7268,7 +7268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="4"/>
       <c r="B106" s="1">
         <v>7</v>
@@ -7286,7 +7286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="4"/>
       <c r="B107" s="1">
         <v>8</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="4"/>
       <c r="B108" s="1">
         <v>9</v>
@@ -7322,7 +7322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="4"/>
       <c r="B109" s="1">
         <v>10</v>
@@ -7340,7 +7340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="4"/>
       <c r="B110" s="1">
         <v>11</v>
@@ -7358,7 +7358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="4"/>
       <c r="B111" s="1">
         <v>12</v>
@@ -7376,7 +7376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="4"/>
       <c r="B112" s="1">
         <v>13</v>
@@ -7394,7 +7394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="4"/>
       <c r="B113" s="1">
         <v>14</v>
@@ -7412,7 +7412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="4"/>
       <c r="B114" s="1">
         <v>15</v>
@@ -7430,7 +7430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="4"/>
       <c r="B115" s="1">
         <v>16</v>
@@ -7448,7 +7448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="4"/>
       <c r="B116" s="1">
         <v>17</v>
@@ -7466,7 +7466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="4"/>
       <c r="B117" s="1">
         <v>18</v>
@@ -7484,7 +7484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="4"/>
       <c r="B118" s="1">
         <v>19</v>
@@ -7502,7 +7502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="4"/>
       <c r="B119" s="1">
         <v>20</v>
@@ -7520,7 +7520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="4"/>
       <c r="B120" s="1">
         <v>21</v>
@@ -7538,7 +7538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="4"/>
       <c r="B121" s="1">
         <v>22</v>
@@ -7556,7 +7556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="4"/>
       <c r="B122" s="1">
         <v>23</v>
@@ -7574,7 +7574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="4"/>
       <c r="B123" s="1">
         <v>24</v>
@@ -7592,7 +7592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
         <v>15</v>
       </c>
@@ -7612,7 +7612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" s="4"/>
       <c r="B125" s="1">
         <v>2</v>
@@ -7630,7 +7630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="4"/>
       <c r="B126" s="1">
         <v>3</v>
@@ -7648,7 +7648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" s="4"/>
       <c r="B127" s="1">
         <v>4</v>
@@ -7666,7 +7666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" s="4"/>
       <c r="B128" s="1">
         <v>5</v>
@@ -7684,7 +7684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" s="4"/>
       <c r="B129" s="1">
         <v>6</v>
@@ -7702,7 +7702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" s="4"/>
       <c r="B130" s="1">
         <v>7</v>
@@ -7720,7 +7720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" s="4"/>
       <c r="B131" s="1">
         <v>8</v>
@@ -7738,7 +7738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" s="4"/>
       <c r="B132" s="1">
         <v>9</v>
@@ -7756,7 +7756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" s="4"/>
       <c r="B133" s="1">
         <v>10</v>
@@ -7774,7 +7774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" s="4"/>
       <c r="B134" s="1">
         <v>11</v>
@@ -7792,7 +7792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" s="4"/>
       <c r="B135" s="1">
         <v>12</v>
@@ -7810,7 +7810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" s="4"/>
       <c r="B136" s="1">
         <v>13</v>
@@ -7828,7 +7828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" s="4"/>
       <c r="B137" s="1">
         <v>14</v>
@@ -7846,7 +7846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" s="4"/>
       <c r="B138" s="1">
         <v>15</v>
@@ -7864,7 +7864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" s="4"/>
       <c r="B139" s="1">
         <v>16</v>
@@ -7882,7 +7882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" s="4"/>
       <c r="B140" s="1">
         <v>17</v>
@@ -7900,7 +7900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" s="4"/>
       <c r="B141" s="1">
         <v>18</v>
@@ -7918,7 +7918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" s="4"/>
       <c r="B142" s="1">
         <v>19</v>
@@ -7936,7 +7936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" s="4"/>
       <c r="B143" s="1">
         <v>20</v>
@@ -7954,7 +7954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" s="4"/>
       <c r="B144" s="1">
         <v>21</v>
@@ -7972,7 +7972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" s="4"/>
       <c r="B145" s="1">
         <v>22</v>
@@ -7990,7 +7990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" s="4"/>
       <c r="B146" s="1">
         <v>23</v>
@@ -8008,7 +8008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" s="4"/>
       <c r="B147" s="1">
         <v>24</v>
@@ -8026,7 +8026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
         <v>16</v>
       </c>
@@ -8046,7 +8046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" s="4"/>
       <c r="B149" s="1">
         <v>2</v>
@@ -8064,7 +8064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" s="4"/>
       <c r="B150" s="1">
         <v>3</v>
@@ -8082,7 +8082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" s="4"/>
       <c r="B151" s="1">
         <v>4</v>
@@ -8100,7 +8100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" s="4"/>
       <c r="B152" s="1">
         <v>5</v>
@@ -8118,7 +8118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" s="4"/>
       <c r="B153" s="1">
         <v>6</v>
@@ -8136,7 +8136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" s="4"/>
       <c r="B154" s="1">
         <v>7</v>
@@ -8154,7 +8154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" s="4"/>
       <c r="B155" s="1">
         <v>8</v>
@@ -8172,7 +8172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156" s="4"/>
       <c r="B156" s="1">
         <v>9</v>
@@ -8190,7 +8190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157" s="4"/>
       <c r="B157" s="1">
         <v>10</v>
@@ -8208,7 +8208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158" s="4"/>
       <c r="B158" s="1">
         <v>11</v>
@@ -8226,7 +8226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A159" s="4"/>
       <c r="B159" s="1">
         <v>12</v>
@@ -8244,7 +8244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160" s="4"/>
       <c r="B160" s="1">
         <v>13</v>
@@ -8262,7 +8262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" s="4"/>
       <c r="B161" s="1">
         <v>14</v>
@@ -8280,7 +8280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" s="4"/>
       <c r="B162" s="1">
         <v>15</v>
@@ -8298,7 +8298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163" s="4"/>
       <c r="B163" s="1">
         <v>16</v>
@@ -8316,7 +8316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164" s="4"/>
       <c r="B164" s="1">
         <v>17</v>
@@ -8334,7 +8334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165" s="4"/>
       <c r="B165" s="1">
         <v>18</v>
@@ -8352,7 +8352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" s="4"/>
       <c r="B166" s="1">
         <v>19</v>
@@ -8370,7 +8370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" s="4"/>
       <c r="B167" s="1">
         <v>20</v>
@@ -8388,7 +8388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" s="4"/>
       <c r="B168" s="1">
         <v>21</v>
@@ -8406,7 +8406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169" s="4"/>
       <c r="B169" s="1">
         <v>22</v>
@@ -8424,7 +8424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170" s="4"/>
       <c r="B170" s="1">
         <v>23</v>
@@ -8442,7 +8442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171" s="4"/>
       <c r="B171" s="1">
         <v>24</v>
@@ -8460,7 +8460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
         <v>17</v>
       </c>
@@ -8480,7 +8480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" s="4"/>
       <c r="B173" s="1">
         <v>2</v>
@@ -8498,7 +8498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" s="4"/>
       <c r="B174" s="1">
         <v>3</v>
@@ -8516,7 +8516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175" s="4"/>
       <c r="B175" s="1">
         <v>4</v>
@@ -8534,7 +8534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176" s="4"/>
       <c r="B176" s="1">
         <v>5</v>
@@ -8552,7 +8552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" s="4"/>
       <c r="B177" s="1">
         <v>6</v>
@@ -8570,7 +8570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178" s="4"/>
       <c r="B178" s="1">
         <v>7</v>
@@ -8588,7 +8588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" s="4"/>
       <c r="B179" s="1">
         <v>8</v>
@@ -8606,7 +8606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" s="4"/>
       <c r="B180" s="1">
         <v>9</v>
@@ -8624,7 +8624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181" s="4"/>
       <c r="B181" s="1">
         <v>10</v>
@@ -8642,7 +8642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182" s="4"/>
       <c r="B182" s="1">
         <v>11</v>
@@ -8660,7 +8660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" s="4"/>
       <c r="B183" s="1">
         <v>12</v>
@@ -8678,7 +8678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184" s="4"/>
       <c r="B184" s="1">
         <v>13</v>
@@ -8696,7 +8696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" s="4"/>
       <c r="B185" s="1">
         <v>14</v>
@@ -8714,7 +8714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" s="4"/>
       <c r="B186" s="1">
         <v>15</v>
@@ -8732,7 +8732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" s="4"/>
       <c r="B187" s="1">
         <v>16</v>
@@ -8750,7 +8750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" s="4"/>
       <c r="B188" s="1">
         <v>17</v>
@@ -8768,7 +8768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" s="4"/>
       <c r="B189" s="1">
         <v>18</v>
@@ -8786,7 +8786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" s="4"/>
       <c r="B190" s="1">
         <v>19</v>
@@ -8804,7 +8804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191" s="4"/>
       <c r="B191" s="1">
         <v>20</v>
@@ -8822,7 +8822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192" s="4"/>
       <c r="B192" s="1">
         <v>21</v>
@@ -8840,7 +8840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" s="4"/>
       <c r="B193" s="1">
         <v>22</v>
@@ -8858,7 +8858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" s="4"/>
       <c r="B194" s="1">
         <v>23</v>
@@ -8876,7 +8876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195" s="4"/>
       <c r="B195" s="1">
         <v>24</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196" s="4" t="s">
         <v>18</v>
       </c>
@@ -8914,7 +8914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" s="4"/>
       <c r="B197" s="1">
         <v>2</v>
@@ -8932,7 +8932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" s="4"/>
       <c r="B198" s="1">
         <v>3</v>
@@ -8950,7 +8950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" s="4"/>
       <c r="B199" s="1">
         <v>4</v>
@@ -8968,7 +8968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" s="4"/>
       <c r="B200" s="1">
         <v>5</v>
@@ -8986,7 +8986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" s="4"/>
       <c r="B201" s="1">
         <v>6</v>
@@ -9004,7 +9004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202" s="4"/>
       <c r="B202" s="1">
         <v>7</v>
@@ -9022,7 +9022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" s="4"/>
       <c r="B203" s="1">
         <v>8</v>
@@ -9040,7 +9040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204" s="4"/>
       <c r="B204" s="1">
         <v>9</v>
@@ -9058,7 +9058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205" s="4"/>
       <c r="B205" s="1">
         <v>10</v>
@@ -9076,7 +9076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206" s="4"/>
       <c r="B206" s="1">
         <v>11</v>
@@ -9094,7 +9094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A207" s="4"/>
       <c r="B207" s="1">
         <v>12</v>
@@ -9112,7 +9112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A208" s="4"/>
       <c r="B208" s="1">
         <v>13</v>
@@ -9130,7 +9130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A209" s="4"/>
       <c r="B209" s="1">
         <v>14</v>
@@ -9148,7 +9148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A210" s="4"/>
       <c r="B210" s="1">
         <v>15</v>
@@ -9166,7 +9166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A211" s="4"/>
       <c r="B211" s="1">
         <v>16</v>
@@ -9184,7 +9184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A212" s="4"/>
       <c r="B212" s="1">
         <v>17</v>
@@ -9202,7 +9202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A213" s="4"/>
       <c r="B213" s="1">
         <v>18</v>
@@ -9220,7 +9220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A214" s="4"/>
       <c r="B214" s="1">
         <v>19</v>
@@ -9238,7 +9238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A215" s="4"/>
       <c r="B215" s="1">
         <v>20</v>
@@ -9256,7 +9256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A216" s="4"/>
       <c r="B216" s="1">
         <v>21</v>
@@ -9274,7 +9274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A217" s="4"/>
       <c r="B217" s="1">
         <v>22</v>
@@ -9292,7 +9292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A218" s="4"/>
       <c r="B218" s="1">
         <v>23</v>
@@ -9310,7 +9310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A219" s="4"/>
       <c r="B219" s="1">
         <v>24</v>
@@ -9328,7 +9328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A220" s="4" t="s">
         <v>19</v>
       </c>
@@ -9348,7 +9348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A221" s="4"/>
       <c r="B221" s="1">
         <v>2</v>
@@ -9366,7 +9366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A222" s="4"/>
       <c r="B222" s="1">
         <v>3</v>
@@ -9384,7 +9384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A223" s="4"/>
       <c r="B223" s="1">
         <v>4</v>
@@ -9402,7 +9402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A224" s="4"/>
       <c r="B224" s="1">
         <v>5</v>
@@ -9420,7 +9420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A225" s="4"/>
       <c r="B225" s="1">
         <v>6</v>
@@ -9438,7 +9438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A226" s="4"/>
       <c r="B226" s="1">
         <v>7</v>
@@ -9456,7 +9456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A227" s="4"/>
       <c r="B227" s="1">
         <v>8</v>
@@ -9474,7 +9474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A228" s="4"/>
       <c r="B228" s="1">
         <v>9</v>
@@ -9492,7 +9492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A229" s="4"/>
       <c r="B229" s="1">
         <v>10</v>
@@ -9510,7 +9510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A230" s="4"/>
       <c r="B230" s="1">
         <v>11</v>
@@ -9528,7 +9528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A231" s="4"/>
       <c r="B231" s="1">
         <v>12</v>
@@ -9546,7 +9546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A232" s="4"/>
       <c r="B232" s="1">
         <v>13</v>
@@ -9564,7 +9564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A233" s="4"/>
       <c r="B233" s="1">
         <v>14</v>
@@ -9582,7 +9582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A234" s="4"/>
       <c r="B234" s="1">
         <v>15</v>
@@ -9600,7 +9600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A235" s="4"/>
       <c r="B235" s="1">
         <v>16</v>
@@ -9618,7 +9618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A236" s="4"/>
       <c r="B236" s="1">
         <v>17</v>
@@ -9636,7 +9636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A237" s="4"/>
       <c r="B237" s="1">
         <v>18</v>
@@ -9654,7 +9654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A238" s="4"/>
       <c r="B238" s="1">
         <v>19</v>
@@ -9672,7 +9672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A239" s="4"/>
       <c r="B239" s="1">
         <v>20</v>
@@ -9690,7 +9690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A240" s="4"/>
       <c r="B240" s="1">
         <v>21</v>
@@ -9708,7 +9708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A241" s="4"/>
       <c r="B241" s="1">
         <v>22</v>
@@ -9726,7 +9726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A242" s="4"/>
       <c r="B242" s="1">
         <v>23</v>
@@ -9744,7 +9744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A243" s="4"/>
       <c r="B243" s="1">
         <v>24</v>
@@ -9783,9 +9783,9 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9800,7 +9800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -9817,12 +9817,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -9839,7 +9839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -9856,7 +9856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -9873,7 +9873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -9890,7 +9890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -9924,7 +9924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -9941,7 +9941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -9958,7 +9958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -9975,7 +9975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -10003,9 +10003,9 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10020,7 +10020,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -10037,12 +10037,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -10059,7 +10059,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -10076,7 +10076,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -10093,7 +10093,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -10110,7 +10110,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -10127,7 +10127,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -10144,7 +10144,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -10161,7 +10161,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -10178,7 +10178,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -10195,7 +10195,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -10223,9 +10223,9 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10240,7 +10240,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -10257,12 +10257,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -10279,7 +10279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -10296,7 +10296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -10313,7 +10313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -10330,7 +10330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -10347,7 +10347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -10364,7 +10364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -10381,7 +10381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -10398,7 +10398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -10415,7 +10415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -10443,16 +10443,16 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10467,7 +10467,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -10484,12 +10484,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -10506,7 +10506,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -10523,7 +10523,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -10540,7 +10540,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -10557,7 +10557,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -10574,7 +10574,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -10591,7 +10591,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -10608,7 +10608,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -10625,7 +10625,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -10642,7 +10642,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -10670,14 +10670,14 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="20.140625" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" customWidth="1"/>
-    <col min="4" max="5" width="20.140625" customWidth="1"/>
+    <col min="1" max="2" width="20.1796875" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" customWidth="1"/>
+    <col min="4" max="5" width="20.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10692,7 +10692,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -10709,12 +10709,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -10731,7 +10731,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -10748,7 +10748,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -10765,7 +10765,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -10782,7 +10782,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -10799,7 +10799,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -10816,7 +10816,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -10833,7 +10833,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -10850,7 +10850,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -10867,7 +10867,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -10895,9 +10895,9 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10909,7 +10909,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -10923,12 +10923,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -10942,7 +10942,7 @@
         <v>1E+20</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -10956,7 +10956,7 @@
         <v>1E+20</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -10970,7 +10970,7 @@
         <v>1E+20</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -10984,7 +10984,7 @@
         <v>1E+20</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -10998,7 +10998,7 @@
         <v>1E+20</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -11012,7 +11012,7 @@
         <v>1E+20</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -11026,7 +11026,7 @@
         <v>1E+20</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -11040,7 +11040,7 @@
         <v>1E+20</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -11054,7 +11054,7 @@
         <v>1E+20</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -11079,9 +11079,9 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11093,7 +11093,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -11107,12 +11107,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -11126,7 +11126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -11140,7 +11140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -11154,7 +11154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -11168,7 +11168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -11182,7 +11182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -11196,7 +11196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -11210,7 +11210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -11224,7 +11224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -11238,7 +11238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -11263,13 +11263,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
-    <col min="2" max="6" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="2" max="6" width="14.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11284,7 +11284,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -11301,12 +11301,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -11325,7 +11325,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -11344,7 +11344,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -11363,7 +11363,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -11382,7 +11382,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -11401,7 +11401,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -11420,7 +11420,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -11439,7 +11439,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -11458,7 +11458,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -11477,7 +11477,7 @@
         <v>1000000000</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -11507,9 +11507,9 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11521,7 +11521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -11535,12 +11535,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -11554,7 +11554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -11568,7 +11568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -11582,7 +11582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -11596,7 +11596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -11610,7 +11610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -11624,7 +11624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -11638,7 +11638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -11652,7 +11652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -11666,7 +11666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -11691,9 +11691,9 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11705,7 +11705,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -11719,12 +11719,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -11738,7 +11738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -11752,7 +11752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -11766,7 +11766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -11780,7 +11780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -11794,7 +11794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -11808,7 +11808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -11822,7 +11822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -11836,7 +11836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -11850,7 +11850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -11875,9 +11875,9 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -11885,7 +11885,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -11893,7 +11893,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -11901,7 +11901,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -11909,7 +11909,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -11917,7 +11917,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -11925,7 +11925,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -11933,7 +11933,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -11941,7 +11941,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -11949,7 +11949,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -11957,7 +11957,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -11973,9 +11973,9 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -11983,7 +11983,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -11991,7 +11991,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -11999,7 +11999,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -12007,7 +12007,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -12015,7 +12015,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -12023,7 +12023,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -12031,7 +12031,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -12039,7 +12039,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -12047,7 +12047,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -12055,7 +12055,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -12071,9 +12071,9 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -12081,7 +12081,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -12089,7 +12089,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -12097,7 +12097,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -12105,7 +12105,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -12113,7 +12113,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -12121,7 +12121,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -12129,7 +12129,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -12137,7 +12137,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -12145,7 +12145,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -12153,7 +12153,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -12169,16 +12169,16 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12193,7 +12193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -12210,12 +12210,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -12232,7 +12232,7 @@
         <v>1E+20</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -12249,7 +12249,7 @@
         <v>1E+20</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -12266,7 +12266,7 @@
         <v>1E+20</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -12283,7 +12283,7 @@
         <v>1E+20</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -12300,7 +12300,7 @@
         <v>1E+20</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -12317,7 +12317,7 @@
         <v>1E+20</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -12334,7 +12334,7 @@
         <v>1E+20</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -12351,7 +12351,7 @@
         <v>1E+20</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -12368,7 +12368,7 @@
         <v>1E+20</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -12396,9 +12396,9 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{133757E7-14E0-4A8B-A539-533F11350980}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12410,7 +12410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -12424,12 +12424,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>38</v>
       </c>
@@ -12454,9 +12454,9 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55A3DC06-1E65-49B0-B373-B79CB8CA87BB}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -12464,7 +12464,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -12472,7 +12472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -12480,7 +12480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -12488,7 +12488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -12496,7 +12496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -12504,7 +12504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -12512,7 +12512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -12528,7 +12528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -12536,7 +12536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -12552,9 +12552,9 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139A5E8D-639A-4006-9AC7-7040FEA74CB9}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -12562,7 +12562,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -12570,7 +12570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -12578,7 +12578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -12586,7 +12586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -12594,7 +12594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -12602,7 +12602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -12610,7 +12610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -12618,7 +12618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -12626,7 +12626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -12634,7 +12634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -12650,13 +12650,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="4" width="19.85546875" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="2" max="4" width="19.81640625" customWidth="1"/>
+    <col min="5" max="5" width="16.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -12667,7 +12667,7 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -12682,7 +12682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -12699,12 +12699,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -12715,13 +12715,13 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -12732,13 +12732,13 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -12749,13 +12749,13 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -12766,13 +12766,13 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -12783,13 +12783,13 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -12800,13 +12800,13 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -12817,13 +12817,13 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -12834,13 +12834,13 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -12851,13 +12851,13 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -12868,7 +12868,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -12886,9 +12886,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12903,7 +12903,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -12920,12 +12920,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -12942,7 +12942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -12959,7 +12959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -12976,7 +12976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -12993,7 +12993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -13010,7 +13010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -13027,7 +13027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -13044,7 +13044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -13061,7 +13061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -13078,7 +13078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -13106,9 +13106,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -13119,7 +13119,7 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -13134,7 +13134,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -13151,12 +13151,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -13173,7 +13173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -13190,7 +13190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -13207,7 +13207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -13224,7 +13224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -13241,7 +13241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -13258,7 +13258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -13275,7 +13275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -13292,7 +13292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -13309,7 +13309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -13338,9 +13338,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -13350,7 +13350,7 @@
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -13362,7 +13362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -13376,12 +13376,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -13395,7 +13395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -13409,7 +13409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -13423,7 +13423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -13437,7 +13437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -13451,7 +13451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -13465,7 +13465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -13479,7 +13479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -13493,7 +13493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -13507,7 +13507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -13533,9 +13533,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
@@ -13552,7 +13552,7 @@
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -13577,7 +13577,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -13606,12 +13606,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -13640,7 +13640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -13669,7 +13669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -13698,7 +13698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -13727,7 +13727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -13756,7 +13756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -13785,7 +13785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -13814,7 +13814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -13843,7 +13843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -13872,7 +13872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -13915,13 +13915,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.5703125" customWidth="1"/>
-    <col min="2" max="5" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="30.54296875" customWidth="1"/>
+    <col min="2" max="5" width="14.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13936,7 +13936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -13953,12 +13953,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>26</v>
       </c>
@@ -13985,6 +13985,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="e67e9a88-35e1-4b39-8da9-a609eb308282" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100241E96938535DD4B921FCDFB54345D30" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a684a74f1c6746079667ad43256762fb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e" xmlns:ns3="e67e9a88-35e1-4b39-8da9-a609eb308282" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb365b527691b54101d88dcd129f0f60" ns2:_="" ns3:_="">
     <xsd:import namespace="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e"/>
@@ -14239,34 +14259,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="e67e9a88-35e1-4b39-8da9-a609eb308282" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{295351A4-E578-46E6-88A7-5B78A2A9DB2F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28704F8A-07C3-40E3-8454-EE1FB7E860CF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e"/>
+    <ds:schemaRef ds:uri="e67e9a88-35e1-4b39-8da9-a609eb308282"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A79F35D8-F94E-474A-814B-A0114ADB6CBF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A79F35D8-F94E-474A-814B-A0114ADB6CBF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28704F8A-07C3-40E3-8454-EE1FB7E860CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{295351A4-E578-46E6-88A7-5B78A2A9DB2F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e"/>
+    <ds:schemaRef ds:uri="e67e9a88-35e1-4b39-8da9-a609eb308282"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>